--- a/public/import/Template soal CBT.xlsx
+++ b/public/import/Template soal CBT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericwahyu/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA2E226-420B-1B42-B52B-8F85A5DA7E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533208E8-B83B-AB4A-AAEA-D1D96311B6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1260" windowWidth="34200" windowHeight="20980" xr2:uid="{D4F72752-1A0A-F54B-8535-D42379D12992}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>Topik Soal</t>
   </si>
@@ -114,13 +114,28 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>Prodi</t>
+  </si>
+  <si>
+    <t>Kedokteran</t>
+  </si>
+  <si>
+    <t>PEMBERITAHUAN
+1. Pastikan Kolom Prodi, Topik Soal, Kategori Materi, dan Materi soal ada di dalam data master pada sistem, jika tidak maka data tersebut akan kosong.
+2. Kolom Tipe Soal harus sesuai dengan tipe yang ada di master data, jika tidak sama maka data soal tidak akan masuk dalam import.
+3. Kolom Soal bersifat wajib diisi.
+4. Kolom Deskripsi berisifat opsional untuk di isi.
+5. Kolom A-E adalah pilihan jawaban untuk soal tersebut dan bersifat wajib diisi.
+6. Kolom Jawaban adalah kunci jawaban dari soal tersebut.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -141,13 +156,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FF49"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -177,18 +203,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF6FF49"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -517,121 +555,317 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA10F97-AAAA-964A-A54A-D638B4672F16}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="P2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>24</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>25</v>
       </c>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+    </row>
+    <row r="17" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+    </row>
+    <row r="18" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+    </row>
+    <row r="19" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+    </row>
+    <row r="20" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+    </row>
+    <row r="21" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+    </row>
+    <row r="22" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+    </row>
+    <row r="23" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+    </row>
+    <row r="24" spans="16:21" x14ac:dyDescent="0.2">
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P2:U24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/public/import/Template soal CBT.xlsx
+++ b/public/import/Template soal CBT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericwahyu/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533208E8-B83B-AB4A-AAEA-D1D96311B6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0A2A62-98EF-6E47-A00D-A32D2E2965E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1260" windowWidth="34200" windowHeight="20980" xr2:uid="{D4F72752-1A0A-F54B-8535-D42379D12992}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{D4F72752-1A0A-F54B-8535-D42379D12992}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>Topik Soal</t>
   </si>
@@ -122,13 +121,17 @@
     <t>Kedokteran</t>
   </si>
   <si>
-    <t>PEMBERITAHUAN
+    <t>Kategori Soal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEMBERITAHUAN
 1. Pastikan Kolom Prodi, Topik Soal, Kategori Materi, dan Materi soal ada di dalam data master pada sistem, jika tidak maka data tersebut akan kosong.
 2. Kolom Tipe Soal harus sesuai dengan tipe yang ada di master data, jika tidak sama maka data soal tidak akan masuk dalam import.
 3. Kolom Soal bersifat wajib diisi.
 4. Kolom Deskripsi berisifat opsional untuk di isi.
 5. Kolom A-E adalah pilihan jawaban untuk soal tersebut dan bersifat wajib diisi.
-6. Kolom Jawaban adalah kunci jawaban dari soal tersebut.</t>
+6. Kolom Jawaban adalah kunci jawaban dari soal tersebut.
+7. Kolom Kategori Soal diisi dengan TWK, TPA, dan TKP </t>
   </si>
 </sst>
 </file>
@@ -203,16 +206,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -562,8 +562,9 @@
     <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -583,31 +584,34 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -620,32 +624,33 @@
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>28</v>
+      <c r="P2" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -663,28 +668,28 @@
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>23</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>25</v>
       </c>
       <c r="P3" s="4"/>
